--- a/02_DIA_inicio_2026_analisis_assets/rbd_9741_escuela-basica-republica-de-indonesia_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9741_escuela-basica-republica-de-indonesia_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5492D312-91A4-43B0-BD0A-A3027A1C65D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4927C2-5FDA-4E5E-98A9-72F3D4916516}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D695CF5A-5FB8-4CAB-A6FB-635E0D361E0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834B11DB-39F8-4587-973A-04CD11263A95}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F3395F4-E090-4D56-B017-91ECD10B963F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AC5A508-43BE-4C2A-9F2E-44F226275F65}"/>
 </file>